--- a/推理框架/cards/vllm-full-session-review-correction.xlsx
+++ b/推理框架/cards/vllm-full-session-review-correction.xlsx
@@ -41,17 +41,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">反向由C++调度，就只能查算子日志吗？</t>
+          <t xml:space="preserve">反向由 C++ 调度时，Python 侧能怎样观察梯度？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话 E11；pytorch v2.11.0</t>
+          <t xml:space="preserve">全会话 E11；PyTorch v2.11.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">不是；例如Tensor.register_hook可在Python侧观察该Tensor的梯度。</t>
+          <t xml:space="preserve">例如使用 Tensor.register_hook，在 Python 侧观察该 Tensor 的梯度。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -61,24 +61,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hook的可观测范围仍需按接口确认；C++调度实现不意味着Python没有反向观测手段。</t>
+          <t xml:space="preserve">• [T#B#原因]：反向调度的实现语言，不决定用户可用的观测接口。
+[T#B,!c47f17#边界]：hook 的可观测范围须按具体接口确认；此卡固定 PyTorch v2.11.0。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">新采样token能立刻计入本步已计算输入吗？</t>
+          <t xml:space="preserve">新采样的 token 在哪一步作为输入计算自身 KV？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">prompt=10、预算=4、前两步已处理8；无命中/投机。全会话 C05</t>
+          <t xml:space="preserve">prompt=10、预算=4、前两步已处理 8；无命中/投机。全会话 C05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不能；它本轮才被采样，通常下一轮才作为输入计算自身KV。</t>
+          <t xml:space="preserve">普通无投机 decode 中，通常在下一步作为输入计算自身 KV。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -88,24 +89,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">原题prompt有10个token、预算4，第三步只剩2个输入；不能把随后采样的新token提前算成该步输入。</t>
+          <t xml:space="preserve">• [T#B#原因]：10-token prompt、预算为 4，前两步已处理 8 个；第三步只计算剩余 2 个输入，随后才采样。
+[T#B,!c47f17#边界]：采样得到 token ID，不等于该 token 的 KV 已经产生。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">只要Core尚未结束，就把请求加入reqs_to_abort吗？</t>
+          <t xml:space="preserve">前端在什么条件下把请求加入 reqs_to_abort？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话 C08；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话 C08；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">不是；还需要前端已经确定该请求结束。</t>
+          <t xml:space="preserve">前端已确定请求结束，而 Core 尚未结束时。</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -115,24 +117,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">原答省略了外层finish_reason条件；普通持续decode不能因此被取消。</t>
+          <t xml:space="preserve">• [T#B#原因]：外层的前端结束条件与内层的 Core 状态条件必须一起读取。
+[T#B,!c47f17#边界]：普通仍在生成的请求不能因此被取消；加入待取消列表与发送 ABORT 是两步。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot_mapping直接决定新KV写入，还是历史KV读取？</t>
+          <t xml:space="preserve">slot_mapping 的直接职责是什么？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话 D04；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话 D04；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接决定新KV写到哪个槽位；历史上下文读取还依赖block table。</t>
+          <t xml:space="preserve">定位本步新 KV 的写入槽位；历史 KV 读取还依赖 block table。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -142,24 +145,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">原答正确要求重排映射，但混合了写入与读取的直接职责；写错KV也会间接污染后续计算。</t>
+          <t xml:space="preserve">• [T#B#原因]：原答正确要求同步重排，但混合了写入定位与读取上下文的直接职责。
+[T#B,!c47f17#边界]：写错 KV 会间接污染后续计算，不能据此把两类映射当成同一件事。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worker每个engine step都重新初始化设备吗？</t>
+          <t xml:space="preserve">Worker 的设备初始化发生在启动时，还是每个 step？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话 R01；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话 R01；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">不需要；设备初始化属于启动阶段，本步经执行入口委托Runner。</t>
+          <t xml:space="preserve">设备初始化属于启动阶段；本步执行由 Worker 入口委托 Runner。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -169,14 +173,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">原话出现在一次SchedulerOutput的执行路径中，混入了服务启动阶段的动作。</t>
+          <t xml:space="preserve">• [T#B#原因]：原话出现在一次 SchedulerOutput 的执行路径中，把启动动作放进了热路径。
+[T#B,!c47f17#边界]：描述每个 step 时，要与服务启动和运维操作分开。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">算子必须保持的契约，只写register_oot够吗？</t>
+          <t xml:space="preserve">算子注册方式为什么不能代替正确性契约？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -186,7 +191,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">不够；还需保持数学语义、tensor行为和执行依赖。</t>
+          <t xml:space="preserve">注册说明如何接入；正确性还要求数学语义、Tensor 行为和执行依赖保持一致。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -196,24 +201,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">原答的注册路径正确，但放进了“必须保持的契约”栏，回答维度不匹配。</t>
+          <t xml:space="preserve">• [T#B#原因]：原答注册路径正确，但填入的是“必须保持的契约”栏，回答维度不匹配。
+[T#B,!c47f17#边界]：注册成功不代表所有 shape、dtype、device、输入修改及返回约定都已验证。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FINAL_ONLY是在Core还是前端抑制中间RequestOutput？</t>
+          <t xml:space="preserve">FINAL_ONLY 在哪一层抑制中间 RequestOutput？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话 R02；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话 R02；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">在前端；Core仍逐步回传内部结果，前端暂不交付中间RequestOutput。</t>
+          <t xml:space="preserve">在前端抑制对调用方的中间输出；Core 仍逐步回传内部结果。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -223,24 +229,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">会话早期导师也给出过不准确的Core粒度解释；以最终核验的OutputProcessor行为为准，不全部归责用户。</t>
+          <t xml:space="preserve">• [T#B#原因]：区分内部结果回传与面向调用方的 RequestOutput 交付。
+[T#B,!c47f17#边界]：导师早期也给过不准确解释；以最终核验的 OutputProcessor 行为为准，不全部归责用户。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">最终输出未被消费，能先注销RequestState吗？</t>
+          <t xml:space="preserve">最终输出已入 Collector，何时可以注销 RequestState？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">最终输出已入Collector，generate尚未消费；讨论RequestState是否必须等它。全会话 R06；vLLM v0.26.0</t>
+          <t xml:space="preserve">最终输出已入 Collector，generate 尚未消费；讨论 RequestState 是否必须等它。全会话 R06；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">可以；最终结果先放入Collector，generate仍持有它并能继续消费。</t>
+          <t xml:space="preserve">最终结果入 Collector 后即可注销；generate 仍持有 Collector 并可继续消费。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -250,24 +257,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">原答把两者绑定在generate消费后一起清理。移除请求表条目不等于强制销毁所有关联对象。</t>
+          <t xml:space="preserve">• [T#B#原因]：请求表条目的生命周期与被其他对象持有的 Collector 生命周期不同。
+[T#B,!c47f17#边界]：移除 RequestState 不等于立即销毁所有关联对象，也不要求等待最终输出被消费。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">结束请求的KV引用由ModelRunner再减少一次吗？</t>
+          <t xml:space="preserve">ModelRunner 收尾时应再次减少 KV 引用计数吗？</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">主语是ModelRunner，调度侧已解除该请求KV引用。全会话 R07；vLLM v0.26.0</t>
+          <t xml:space="preserve">主语是 ModelRunner，调度侧已解除该请求 KV 引用。全会话 R07；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">不能；调度侧已解除引用，Runner只清自己的请求和batch状态。</t>
+          <t xml:space="preserve">不应再次扣减；调度侧已解除引用，Runner 只清自己的请求和 batch 状态。</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -277,24 +285,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">原题中的“它”指ModelRunner。重复扣减会让仍被其他请求使用的共享块错误归零。</t>
+          <t xml:space="preserve">• [T#B#原因]：原题主语是 ModelRunner；重复扣减可能让其他请求仍使用的共享块错误归零。
+[T#B,!c47f17#边界]：Runner 请求状态清理与调度侧 KV 引用管理是不同职责。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">前端stop string判停，给Core发送的操作是什么？</t>
+          <t xml:space="preserve">前端因 stop string 判停时，向 Core 发送什么操作？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">全会话 R05；vllm v0.26.0</t>
+          <t xml:space="preserve">全会话 R05；vLLM v0.26.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">向尚未结束的Core发送ABORT；对用户仍可报告stop。</t>
+          <t xml:space="preserve">向尚未结束的 Core 发送 ABORT；对用户仍可报告 stop。</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -304,7 +313,8 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">用户可见finish reason与内部控制操作属于不同语义层。</t>
+          <t xml:space="preserve">• [T#B#原因]：用户可见的结束原因与内部控制操作属于不同语义层。
+[T#B,!c47f17#边界]：若 Core 已结束，不重复发送取消操作。</t>
         </is>
       </c>
     </row>
